--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AIRBAG-CSTD-1-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AIRBAG-CSTD-1-01-A-C0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\shamoto\Sprint62\設計書\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAAC37F3-5C91-4F6B-83F3-089974E2C38B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14250" windowHeight="10010"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,17 +22,30 @@
     <sheet name="Reference" sheetId="3" r:id="rId7"/>
     <sheet name="History" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,12 +99,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -152,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -207,13 +221,13 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -228,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="1" shapeId="0">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -271,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -292,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -307,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0">
+    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -323,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -339,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="1" shapeId="0">
+    <comment ref="L2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="1" shapeId="0">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -374,13 +388,13 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -397,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="1" shapeId="0">
+    <comment ref="C9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -413,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0">
+    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="1" shapeId="0">
+    <comment ref="F9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -444,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0">
+    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -460,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -476,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="1" shapeId="0">
+    <comment ref="I9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -492,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
       <text>
         <r>
           <rPr>
@@ -512,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2504" uniqueCount="289">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2483,14 +2497,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ABG1S01_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ABG1S01_STS</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>PRMRYCHK</t>
   </si>
   <si>
@@ -2555,10 +2561,6 @@
   </si>
   <si>
     <t>VOM</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ABG1S01</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2860,11 +2862,19 @@
 ・各キャプチャ画像を1A仕様書の画像に変更</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>PDS1S01_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>PDS1S01</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="21">
     <font>
       <sz val="11"/>
@@ -4881,37 +4891,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4956,10 +4945,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5021,21 +5031,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -5092,16 +5088,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -5146,7 +5132,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -5935,7 +5927,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2"/>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -5979,7 +5977,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="図 49"/>
+        <xdr:cNvPr id="50" name="図 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000032000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -6034,7 +6038,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="図 48"/>
+        <xdr:cNvPr id="49" name="図 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000031000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -6089,7 +6099,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="48" name="図 47"/>
+        <xdr:cNvPr id="48" name="図 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000030000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -6144,7 +6160,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="47" name="図 46"/>
+        <xdr:cNvPr id="47" name="図 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
         </xdr:cNvPicPr>
@@ -6199,7 +6221,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22"/>
+        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6318,7 +6346,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="正方形/長方形 24"/>
+        <xdr:cNvPr id="25" name="正方形/長方形 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000019000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6378,7 +6412,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="線吹き出し 1 (枠付き) 25"/>
+        <xdr:cNvPr id="26" name="線吹き出し 1 (枠付き) 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6492,7 +6532,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="正方形/長方形 28"/>
+        <xdr:cNvPr id="29" name="正方形/長方形 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6552,7 +6598,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="線吹き出し 1 (枠付き) 29"/>
+        <xdr:cNvPr id="30" name="線吹き出し 1 (枠付き) 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6635,7 +6687,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="正方形/長方形 30"/>
+        <xdr:cNvPr id="31" name="正方形/長方形 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6695,7 +6753,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="正方形/長方形 34"/>
+        <xdr:cNvPr id="35" name="正方形/長方形 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000023000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6755,7 +6819,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="正方形/長方形 35"/>
+        <xdr:cNvPr id="36" name="正方形/長方形 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000024000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6815,7 +6885,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="正方形/長方形 36"/>
+        <xdr:cNvPr id="37" name="正方形/長方形 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000025000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6875,7 +6951,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="線吹き出し 1 (枠付き) 37"/>
+        <xdr:cNvPr id="38" name="線吹き出し 1 (枠付き) 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000026000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6958,7 +7040,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38"/>
+        <xdr:cNvPr id="39" name="線吹き出し 1 (枠付き) 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000027000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7072,7 +7160,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="正方形/長方形 39"/>
+        <xdr:cNvPr id="40" name="正方形/長方形 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7132,7 +7226,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="線吹き出し 1 (枠付き) 41"/>
+        <xdr:cNvPr id="42" name="線吹き出し 1 (枠付き) 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7215,7 +7315,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="43" name="正方形/長方形 42"/>
+        <xdr:cNvPr id="43" name="正方形/長方形 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7275,7 +7381,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="線吹き出し 1 (枠付き) 51"/>
+        <xdr:cNvPr id="52" name="線吹き出し 1 (枠付き) 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000034000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7358,7 +7470,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="53" name="線吹き出し 1 (枠付き) 52"/>
+        <xdr:cNvPr id="53" name="線吹き出し 1 (枠付き) 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000035000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7485,7 +7603,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43"/>
+        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7596,7 +7720,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="正方形/長方形 60"/>
+        <xdr:cNvPr id="61" name="正方形/長方形 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7656,7 +7786,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="62" name="線吹き出し 1 (枠付き) 61"/>
+        <xdr:cNvPr id="62" name="線吹き出し 1 (枠付き) 61">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7827,7 +7963,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="正方形/長方形 62"/>
+        <xdr:cNvPr id="63" name="正方形/長方形 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7887,7 +8029,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="64" name="正方形/長方形 63"/>
+        <xdr:cNvPr id="64" name="正方形/長方形 63">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000040000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7947,7 +8095,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="65" name="線吹き出し 1 (枠付き) 64"/>
+        <xdr:cNvPr id="65" name="線吹き出し 1 (枠付き) 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000041000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8118,7 +8272,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="67" name="正方形/長方形 66"/>
+        <xdr:cNvPr id="67" name="正方形/長方形 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000043000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8178,7 +8338,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="68" name="線吹き出し 1 (枠付き) 67"/>
+        <xdr:cNvPr id="68" name="線吹き出し 1 (枠付き) 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000044000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8294,7 +8460,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53"/>
+        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8391,7 +8563,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="線吹き出し 1 (枠付き) 40"/>
+        <xdr:cNvPr id="41" name="線吹き出し 1 (枠付き) 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000029000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8474,7 +8652,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44"/>
+        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8585,7 +8769,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8614,13 +8804,565 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>466841</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>131934</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>243570</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>162378</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{61CFCFC0-A897-4F19-B0C1-53D14A783BAF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13853008" y="11265083"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 101846"/>
+            <a:gd name="adj4" fmla="val 317094"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>PDS1S01</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ABG1S01</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>202975</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>91340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>608923</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>60893</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2C4A1A9A-262A-426F-B7E7-37730BE864C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21018007" y="12198767"/>
+          <a:ext cx="1025021" cy="781451"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>60893</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>81190</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>598774</xdr:colOff>
+      <xdr:row>131</xdr:row>
+      <xdr:rowOff>50743</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4C9D6F4-DD69-46FA-9BA4-A285B4312527}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20256853" y="22256151"/>
+          <a:ext cx="1776026" cy="781451"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>91337</xdr:colOff>
+      <xdr:row>119</xdr:row>
+      <xdr:rowOff>60892</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>487138</xdr:colOff>
+      <xdr:row>126</xdr:row>
+      <xdr:rowOff>91337</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4662D751-5FE7-4B13-95BF-1347CB55E5FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14096576" y="21099196"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 116629"/>
+            <a:gd name="adj4" fmla="val 275202"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>PDS1S01</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>ABG1S01</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8658,9 +9400,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8695,7 +9437,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8730,7 +9472,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8903,16 +9645,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -8982,7 +9724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
       <c r="C7" s="221" t="s">
         <v>0</v>
@@ -9062,7 +9804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="13.5" thickTop="1">
+    <row r="9" spans="2:18" ht="13.6" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -9098,13 +9840,13 @@
         <v>31</v>
       </c>
       <c r="M9" s="14" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N9" s="217">
         <v>43943</v>
       </c>
       <c r="O9" s="14" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="P9" s="217">
         <v>43943</v>
@@ -9116,16 +9858,16 @@
         <v>43923</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="78">
+    <row r="10" spans="2:18" ht="77.45">
       <c r="B10" s="10">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D10" s="219" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>212</v>
@@ -9156,7 +9898,7 @@
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="R10" s="220">
         <v>44162</v>
@@ -9206,7 +9948,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" ht="13.5" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9239,22 +9981,25 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9268,13 +10013,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="146" t="s">
         <v>129</v>
       </c>
       <c r="C6" s="146"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="74" t="s">
         <v>131</v>
       </c>
@@ -9294,7 +10039,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="25.85">
       <c r="C9" s="156">
         <v>1</v>
       </c>
@@ -9305,7 +10050,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="154"/>
       <c r="D10" s="85"/>
       <c r="E10" s="6"/>
@@ -9313,14 +10058,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="152"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="147" t="s">
         <v>130</v>
       </c>
       <c r="C12" s="81"/>
       <c r="D12" s="81"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="148"/>
       <c r="C13" s="153" t="s">
         <v>131</v>
@@ -9332,7 +10077,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="150">
         <v>0</v>
       </c>
@@ -9409,17 +10154,17 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="154"/>
       <c r="D21" s="85"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="146" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="153" t="s">
         <v>131</v>
       </c>
@@ -9441,7 +10186,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="151">
         <v>1</v>
       </c>
@@ -9506,12 +10251,12 @@
       <c r="D33" s="84"/>
       <c r="E33" s="70"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="154"/>
       <c r="D34" s="85"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="146" t="s">
         <v>163</v>
       </c>
@@ -9523,7 +10268,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="232"/>
       <c r="D39" s="233"/>
       <c r="E39" s="6" t="s">
@@ -9537,147 +10282,150 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="259" t="s">
+      <c r="B2" s="234" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="260"/>
-      <c r="D2" s="247" t="s">
-        <v>286</v>
-      </c>
-      <c r="E2" s="248"/>
-      <c r="F2" s="248"/>
-      <c r="G2" s="248"/>
-      <c r="H2" s="249"/>
+      <c r="C2" s="235"/>
+      <c r="D2" s="240" t="s">
+        <v>283</v>
+      </c>
+      <c r="E2" s="241"/>
+      <c r="F2" s="241"/>
+      <c r="G2" s="241"/>
+      <c r="H2" s="242"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="234" t="s">
+      <c r="B3" s="236" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="235"/>
-      <c r="D3" s="250" t="s">
-        <v>287</v>
-      </c>
-      <c r="E3" s="251"/>
-      <c r="F3" s="251"/>
-      <c r="G3" s="251"/>
-      <c r="H3" s="252"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="245" t="s">
+      <c r="C3" s="237"/>
+      <c r="D3" s="243" t="s">
+        <v>284</v>
+      </c>
+      <c r="E3" s="244"/>
+      <c r="F3" s="244"/>
+      <c r="G3" s="244"/>
+      <c r="H3" s="245"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="238" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="246"/>
-      <c r="D4" s="253" t="str">
+      <c r="C4" s="239"/>
+      <c r="D4" s="246" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_AIRBAG-CSTD-1-01-A-C0.c</v>
       </c>
-      <c r="E4" s="254"/>
-      <c r="F4" s="254"/>
-      <c r="G4" s="254"/>
-      <c r="H4" s="255"/>
-    </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E4" s="247"/>
+      <c r="F4" s="247"/>
+      <c r="G4" s="247"/>
+      <c r="H4" s="248"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="259" t="s">
+      <c r="B6" s="234" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="260"/>
-      <c r="D6" s="256" t="str">
+      <c r="C6" s="235"/>
+      <c r="D6" s="249" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_AIRBAG</v>
       </c>
-      <c r="E6" s="257"/>
-      <c r="F6" s="257"/>
-      <c r="G6" s="257"/>
-      <c r="H6" s="258"/>
+      <c r="E6" s="250"/>
+      <c r="F6" s="250"/>
+      <c r="G6" s="250"/>
+      <c r="H6" s="251"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="234" t="s">
+      <c r="B7" s="236" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="235"/>
-      <c r="D7" s="236">
+      <c r="C7" s="237"/>
+      <c r="D7" s="252">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="237"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="238"/>
+      <c r="E7" s="253"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="254"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="234" t="s">
+      <c r="B8" s="236" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="235"/>
-      <c r="D8" s="236" t="str">
+      <c r="C8" s="237"/>
+      <c r="D8" s="252" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_AIRBAG_MTRX</v>
       </c>
-      <c r="E8" s="237"/>
-      <c r="F8" s="237"/>
-      <c r="G8" s="237"/>
-      <c r="H8" s="238"/>
+      <c r="E8" s="253"/>
+      <c r="F8" s="253"/>
+      <c r="G8" s="253"/>
+      <c r="H8" s="254"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="234" t="s">
+      <c r="B9" s="236" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="235"/>
-      <c r="D9" s="239" t="s">
+      <c r="C9" s="237"/>
+      <c r="D9" s="255" t="s">
         <v>200</v>
       </c>
-      <c r="E9" s="240"/>
-      <c r="F9" s="240"/>
-      <c r="G9" s="240"/>
-      <c r="H9" s="241"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="245" t="s">
+      <c r="E9" s="256"/>
+      <c r="F9" s="256"/>
+      <c r="G9" s="256"/>
+      <c r="H9" s="257"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="238" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="246"/>
-      <c r="D10" s="242">
+      <c r="C10" s="239"/>
+      <c r="D10" s="258">
         <v>87</v>
       </c>
-      <c r="E10" s="243"/>
-      <c r="F10" s="243"/>
-      <c r="G10" s="243"/>
-      <c r="H10" s="244"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+      <c r="E10" s="259"/>
+      <c r="F10" s="259"/>
+      <c r="G10" s="259"/>
+      <c r="H10" s="260"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="137" t="s">
         <v>34</v>
       </c>
@@ -9712,7 +10460,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="103">
         <v>1</v>
       </c>
@@ -10565,7 +11313,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="94">
         <v>25</v>
       </c>
@@ -10606,80 +11354,83 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="9" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="8" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$K$13:$K$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$13:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="D3" r:id="rId1" display="https://aip01.dndev.net/svn/aip/toyota/rd/spec/tags/800B/00.Product/v2.0.4/ECU/MET/"/>
-    <hyperlink ref="D3:H3" r:id="rId2" display="https://aip01.dndev.net/svn/aip/toyota/rd/spec/tags/800B/00.Product/v2.0.4/ECU/MET/"/>
+    <hyperlink ref="D3" r:id="rId1" display="https://aip01.dndev.net/svn/aip/toyota/rd/spec/tags/800B/00.Product/v2.0.4/ECU/MET/" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="D3:H3" r:id="rId2" display="https://aip01.dndev.net/svn/aip/toyota/rd/spec/tags/800B/00.Product/v2.0.4/ECU/MET/" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>188</v>
       </c>
@@ -10687,7 +11438,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="137" t="s">
         <v>34</v>
       </c>
@@ -10725,7 +11476,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="167">
         <v>0</v>
       </c>
@@ -10753,7 +11504,7 @@
       </c>
       <c r="R4" s="136"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="170">
         <v>1</v>
       </c>
@@ -11281,7 +12032,7 @@
       <c r="Q28" s="141"/>
       <c r="R28" s="113"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="171">
         <v>25</v>
       </c>
@@ -11303,7 +12054,7 @@
       <c r="Q29" s="139"/>
       <c r="R29" s="115"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>189</v>
       </c>
@@ -11311,7 +12062,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="137" t="s">
         <v>34</v>
       </c>
@@ -11343,7 +12094,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="167">
         <v>0</v>
       </c>
@@ -11369,7 +12120,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="170">
         <v>1</v>
       </c>
@@ -11897,7 +12648,7 @@
       <c r="Q58" s="141"/>
       <c r="R58" s="172"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="171">
         <v>25</v>
       </c>
@@ -11926,48 +12677,51 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"OPT,HW"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"DEF"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="28.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="28.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="87" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="95" t="s">
         <v>58</v>
       </c>
@@ -12011,7 +12765,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="46" t="s">
         <v>108</v>
@@ -12032,7 +12786,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="26" t="s">
         <v>207</v>
       </c>
@@ -12058,7 +12812,7 @@
         <v>126</v>
       </c>
       <c r="J4" s="187" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="K4" s="186" t="s">
         <v>126</v>
@@ -12322,7 +13076,7 @@
       </c>
       <c r="U12" s="29"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="112"/>
@@ -14573,7 +15327,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="48"/>
       <c r="C103" s="49"/>
       <c r="D103" s="114"/>
@@ -14604,33 +15358,31 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M103">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B103</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Config_IF!$C$4:$C$29</xm:f>
           </x14:formula1>
@@ -14643,23 +15395,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14778,7 +15530,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="218" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
@@ -14869,11 +15621,11 @@
         <v>62</v>
       </c>
       <c r="AF3" s="269" t="s">
-        <v>214</v>
+        <v>287</v>
       </c>
       <c r="AG3" s="270"/>
       <c r="AH3" s="271" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AI3" s="270"/>
       <c r="AJ3" s="264"/>
@@ -14881,7 +15633,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="265" t="s">
         <v>63</v>
       </c>
@@ -14929,7 +15681,7 @@
       <c r="AV4" s="77"/>
       <c r="AW4" s="78"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="267"/>
       <c r="B5" s="268"/>
       <c r="C5" s="135"/>
@@ -15492,7 +16244,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="25" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -16446,7 +17198,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="131"/>
       <c r="C17" s="42">
         <f t="shared" si="2"/>
@@ -22826,7 +23578,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="51" t="s">
         <v>64</v>
       </c>
@@ -43420,33 +44172,28 @@
     <mergeCell ref="AH3:AI3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D22:AI69 D6:AE21">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+  <conditionalFormatting sqref="D6:AI69">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="2" priority="5">
+    <cfRule type="expression" dxfId="0" priority="5">
       <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF6:AI21">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -43459,24 +44206,24 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AZ226"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="2" max="2" width="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="30.453125" customWidth="1"/>
+    <col min="12" max="12" width="30.5" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="10.90625" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:52" ht="14.5" thickBot="1">
+    <row r="2" spans="2:52" ht="15.65" thickBot="1">
       <c r="B2" s="27" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="V2" s="184" t="s">
         <v>203</v>
@@ -43512,9 +44259,9 @@
       <c r="AY2" s="184"/>
       <c r="AZ2" s="184"/>
     </row>
-    <row r="3" spans="2:52" ht="14.5" thickBot="1">
+    <row r="3" spans="2:52" ht="15.65" thickBot="1">
       <c r="B3" s="92" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C3" s="276" t="s">
         <v>198</v>
@@ -43537,7 +44284,7 @@
     <row r="4" spans="2:52">
       <c r="B4" s="65"/>
       <c r="C4" s="32" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D4" s="32"/>
       <c r="E4" s="32"/>
@@ -43549,7 +44296,7 @@
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
       <c r="M4" s="28" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="N4" s="38" t="s">
         <v>21</v>
@@ -43563,7 +44310,7 @@
         <v>22</v>
       </c>
       <c r="C5" s="272" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D5" s="273"/>
       <c r="E5" s="273"/>
@@ -43573,75 +44320,75 @@
       <c r="I5" s="273"/>
       <c r="J5" s="274"/>
       <c r="K5" s="189" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="L5" s="189"/>
       <c r="M5" s="29" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="N5" s="201" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="O5" s="201" t="s">
         <v>162</v>
       </c>
       <c r="P5" s="72" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Q5" s="191" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="6" spans="2:52" ht="26">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="6" spans="2:52" ht="25.85">
       <c r="B6" s="66" t="s">
         <v>33</v>
       </c>
       <c r="C6" s="159" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="159" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="159" t="s">
+        <v>224</v>
+      </c>
+      <c r="F6" s="159" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" s="159" t="s">
+        <v>225</v>
+      </c>
+      <c r="H6" s="159" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" s="159" t="s">
+        <v>225</v>
+      </c>
+      <c r="J6" s="159" t="s">
+        <v>224</v>
+      </c>
+      <c r="K6" s="202" t="s">
         <v>226</v>
       </c>
-      <c r="D6" s="159" t="s">
+      <c r="L6" s="203" t="s">
+        <v>226</v>
+      </c>
+      <c r="M6" s="29" t="s">
         <v>227</v>
-      </c>
-      <c r="E6" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="F6" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="G6" s="159" t="s">
-        <v>227</v>
-      </c>
-      <c r="H6" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="I6" s="159" t="s">
-        <v>227</v>
-      </c>
-      <c r="J6" s="159" t="s">
-        <v>226</v>
-      </c>
-      <c r="K6" s="202" t="s">
-        <v>228</v>
-      </c>
-      <c r="L6" s="203" t="s">
-        <v>228</v>
-      </c>
-      <c r="M6" s="29" t="s">
-        <v>229</v>
       </c>
       <c r="N6" s="204"/>
       <c r="O6" s="204"/>
       <c r="P6" s="73"/>
       <c r="Q6" s="191" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="7" spans="2:52" ht="26">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="2:52" ht="25.85">
       <c r="B7" s="67" t="s">
         <v>27</v>
       </c>
       <c r="C7" s="275" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D7" s="273"/>
       <c r="E7" s="273"/>
@@ -43651,52 +44398,52 @@
       <c r="I7" s="273"/>
       <c r="J7" s="274"/>
       <c r="K7" s="190" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="L7" s="205" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="M7" s="30"/>
       <c r="N7" s="204"/>
       <c r="O7" s="204"/>
       <c r="P7" s="73"/>
       <c r="Q7" s="181" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="8" spans="2:52" ht="62">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="8" spans="2:52" ht="61.15">
       <c r="B8" s="66" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="206" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D8" s="206" t="s">
         <v>62</v>
       </c>
       <c r="E8" s="206" t="s">
+        <v>231</v>
+      </c>
+      <c r="F8" s="206" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="206" t="s">
+        <v>233</v>
+      </c>
+      <c r="H8" s="206" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="206" t="s">
+      <c r="I8" s="206" t="s">
         <v>235</v>
       </c>
-      <c r="G8" s="206" t="s">
+      <c r="J8" s="206" t="s">
         <v>236</v>
       </c>
-      <c r="H8" s="206" t="s">
-        <v>237</v>
-      </c>
-      <c r="I8" s="206" t="s">
-        <v>238</v>
-      </c>
-      <c r="J8" s="206" t="s">
-        <v>239</v>
-      </c>
       <c r="K8" s="190" t="s">
-        <v>213</v>
+        <v>287</v>
       </c>
       <c r="L8" s="205" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="M8" s="29" t="s">
         <v>29</v>
@@ -43705,60 +44452,60 @@
       <c r="O8" s="204"/>
       <c r="P8" s="73"/>
       <c r="Q8" s="181" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="9" spans="2:52" ht="65.5" thickBot="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="2:52" ht="65.25" thickBot="1">
       <c r="B9" s="68" t="s">
         <v>30</v>
       </c>
       <c r="C9" s="160" t="s">
+        <v>238</v>
+      </c>
+      <c r="D9" s="160" t="s">
+        <v>225</v>
+      </c>
+      <c r="E9" s="160" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" s="160" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" s="160" t="s">
+        <v>237</v>
+      </c>
+      <c r="H9" s="160" t="s">
+        <v>238</v>
+      </c>
+      <c r="I9" s="160" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" s="160" t="s">
+        <v>238</v>
+      </c>
+      <c r="K9" s="192" t="s">
+        <v>239</v>
+      </c>
+      <c r="L9" s="207" t="s">
+        <v>240</v>
+      </c>
+      <c r="M9" s="31" t="s">
         <v>241</v>
       </c>
-      <c r="D9" s="160" t="s">
-        <v>227</v>
-      </c>
-      <c r="E9" s="160" t="s">
-        <v>240</v>
-      </c>
-      <c r="F9" s="160" t="s">
-        <v>241</v>
-      </c>
-      <c r="G9" s="160" t="s">
-        <v>240</v>
-      </c>
-      <c r="H9" s="160" t="s">
-        <v>241</v>
-      </c>
-      <c r="I9" s="160" t="s">
-        <v>241</v>
-      </c>
-      <c r="J9" s="160" t="s">
-        <v>241</v>
-      </c>
-      <c r="K9" s="192" t="s">
+      <c r="N9" s="208" t="s">
         <v>242</v>
       </c>
-      <c r="L9" s="207" t="s">
-        <v>243</v>
-      </c>
-      <c r="M9" s="31" t="s">
-        <v>244</v>
-      </c>
-      <c r="N9" s="208" t="s">
-        <v>245</v>
-      </c>
       <c r="O9" s="208" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="P9" s="71"/>
       <c r="Q9" s="209" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="10" spans="2:52" ht="13.5" thickTop="1">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="2:52" ht="13.6" thickTop="1">
       <c r="B10" s="69" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C10" s="161" t="s">
         <v>161</v>
@@ -43785,13 +44532,13 @@
         <v>161</v>
       </c>
       <c r="K10" s="126" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="L10" s="210" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="N10" s="33" t="s">
         <v>31</v>
@@ -43801,12 +44548,12 @@
       </c>
       <c r="P10" s="36"/>
       <c r="Q10" s="193" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" spans="2:52">
       <c r="B11" s="23" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C11" s="162" t="s">
         <v>161</v>
@@ -43833,19 +44580,19 @@
         <v>161</v>
       </c>
       <c r="K11" s="56" t="s">
+        <v>246</v>
+      </c>
+      <c r="L11" s="211" t="s">
         <v>249</v>
       </c>
-      <c r="L11" s="211" t="s">
+      <c r="M11" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="N11" s="212" t="s">
+        <v>251</v>
+      </c>
+      <c r="O11" s="212" t="s">
         <v>252</v>
-      </c>
-      <c r="M11" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="N11" s="212" t="s">
-        <v>254</v>
-      </c>
-      <c r="O11" s="212" t="s">
-        <v>255</v>
       </c>
       <c r="P11" s="37"/>
       <c r="Q11" s="213" t="s">
@@ -43854,7 +44601,7 @@
     </row>
     <row r="12" spans="2:52">
       <c r="B12" s="23" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C12" s="162" t="s">
         <v>161</v>
@@ -43881,10 +44628,10 @@
         <v>161</v>
       </c>
       <c r="K12" s="56" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="L12" s="211" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="M12" s="35" t="s">
         <v>32</v>
@@ -43897,12 +44644,12 @@
       </c>
       <c r="P12" s="37"/>
       <c r="Q12" s="213" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" spans="2:52">
       <c r="B13" s="23" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C13" s="162" t="s">
         <v>161</v>
@@ -43929,28 +44676,28 @@
         <v>161</v>
       </c>
       <c r="K13" s="56" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L13" s="211" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="N13" s="212" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="O13" s="212" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="P13" s="37"/>
       <c r="Q13" s="213" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="2:52">
       <c r="B14" s="23" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C14" s="162" t="s">
         <v>161</v>
@@ -43977,10 +44724,10 @@
         <v>161</v>
       </c>
       <c r="K14" s="56" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="L14" s="211" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M14" s="35" t="s">
         <v>32</v>
@@ -43993,12 +44740,12 @@
       </c>
       <c r="P14" s="214"/>
       <c r="Q14" s="213" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="2:52">
       <c r="B15" s="23" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C15" s="162" t="s">
         <v>161</v>
@@ -44025,28 +44772,28 @@
         <v>161</v>
       </c>
       <c r="K15" s="56" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L15" s="211" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M15" s="35" t="s">
         <v>202</v>
       </c>
       <c r="N15" s="185" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O15" s="185" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P15" s="214"/>
       <c r="Q15" s="213" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="2:52">
       <c r="B16" s="23" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C16" s="162" t="s">
         <v>161</v>
@@ -44073,28 +44820,28 @@
         <v>161</v>
       </c>
       <c r="K16" s="56" t="s">
+        <v>258</v>
+      </c>
+      <c r="L16" s="211" t="s">
         <v>261</v>
-      </c>
-      <c r="L16" s="211" t="s">
-        <v>264</v>
       </c>
       <c r="M16" s="35" t="s">
         <v>202</v>
       </c>
       <c r="N16" s="185" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="O16" s="185" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="P16" s="214"/>
       <c r="Q16" s="213" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="17" spans="2:17" ht="13.5" thickBot="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" ht="13.6" thickBot="1">
       <c r="B17" s="194" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C17" s="195" t="s">
         <v>161</v>
@@ -44121,10 +44868,10 @@
         <v>161</v>
       </c>
       <c r="K17" s="198" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L17" s="215" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M17" s="197" t="s">
         <v>32</v>
@@ -44137,7 +44884,7 @@
       </c>
       <c r="P17" s="216"/>
       <c r="Q17" s="199" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="22:52">
@@ -44177,7 +44924,7 @@
     </row>
     <row r="140" spans="22:52">
       <c r="V140" s="183" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="W140" s="184"/>
       <c r="X140" s="184"/>
@@ -44246,28 +44993,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="80" t="s">
         <v>85</v>
       </c>
@@ -44277,7 +45027,7 @@
       </c>
       <c r="D2" s="81"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="74" t="s">
         <v>85</v>
       </c>
@@ -44288,7 +45038,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -44299,7 +45049,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -44310,7 +45060,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -44321,7 +45071,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -44332,7 +45082,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -44343,7 +45093,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -44354,7 +45104,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -44365,7 +45115,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -44376,7 +45126,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -44387,7 +45137,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -44398,7 +45148,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -44409,7 +45159,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -44431,7 +45181,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -44442,7 +45192,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -44453,7 +45203,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -44464,7 +45214,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -44486,26 +45236,26 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D22" s="86" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="26">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D23" s="86" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -44523,7 +45273,7 @@
       <c r="C26" s="84"/>
       <c r="D26" s="70"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="85"/>
       <c r="D27" s="6"/>
@@ -44532,5 +45282,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AIRBAG-CSTD-1-01-A-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_B_AIRBAG-CSTD-1-01-A-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9767C260-6D62-4FB6-B198-8E84B83D9684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9099186A-C86F-43BA-AB9A-D239F1F4323D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14535" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3510" yWindow="2130" windowWidth="22740" windowHeight="14070" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -28,7 +28,6 @@
     <externalReference r:id="rId11"/>
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
   </externalReferences>
   <definedNames>
     <definedName name="_1AB030_" localSheetId="0" hidden="1">{"A",#N/A,FALSE,"(部)工程別 ";"B",#N/A,FALSE,"(部)工程別 ";"D",#N/A,FALSE,"(部)工程別 "}</definedName>
@@ -75,8 +74,8 @@
     <definedName name="IG">#REF!</definedName>
     <definedName name="K">#REF!</definedName>
     <definedName name="LED">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area">[3]Sheet1!$A$1:$I$233</definedName>
-    <definedName name="_xlnm.Print_Titles">[4]車両仕様!$A$1:$C$65536,[4]車両仕様!$A$3:$IV$4</definedName>
+    <definedName name="_xlnm.Print_Area">[2]Sheet1!$A$1:$I$233</definedName>
+    <definedName name="_xlnm.Print_Titles">[3]車両仕様!$A$1:$C$65536,[3]車両仕様!$A$3:$IV$4</definedName>
     <definedName name="ｓ">#REF!</definedName>
     <definedName name="Sheet_dspmaincfg_Top">#REF!</definedName>
     <definedName name="Sheet_ユーザーカスタマイズ手順_Top">#REF!</definedName>
@@ -192,16 +191,16 @@
     <definedName name="愛" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="開発費" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
     <definedName name="開発費" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
-    <definedName name="関数名_確定_BON">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGOFF">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGON">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_WKUP">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_0">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_1">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_2">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_3">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_4">'[5]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_定期">'[5]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_BON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGOFF">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_WKUP">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_0">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_1">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_2">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_3">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_4">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_定期">'[4]Config - dspmgr'!#REF!</definedName>
     <definedName name="金型共通化" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化２" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
@@ -722,7 +721,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2571" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2573" uniqueCount="313">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3233,6 +3232,25 @@
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>1.3.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -4692,7 +4710,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="308">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5357,20 +5375,92 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="78" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -5411,37 +5501,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5486,10 +5555,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="67" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="60" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5545,63 +5635,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="30" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="63" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="82" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="28" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -10133,6 +10166,279 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC76BADF-64DF-41F8-9B1C-94F6D317303C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13944600" y="895350"/>
+          <a:ext cx="828675" cy="3762375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>209551</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D84D9EB3-DA35-D192-3DCB-371C0331A4FA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14801850" y="190501"/>
+          <a:ext cx="2752725" cy="914400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>139</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>58</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>182</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F8538C5-6527-43CD-AD26-0D5E2715BF7B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="17597438" y="24931689"/>
+          <a:ext cx="25550812" cy="7167562"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -10442,56 +10748,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="表紙（承認欄）"/>
-      <sheetName val="変更履歴"/>
-      <sheetName val="要件分析, ソフト分析"/>
-      <sheetName val="課題リスト"/>
-      <sheetName val="MAPPING(Featureのみ)"/>
-      <sheetName val="Evidence(Featureのみ)"/>
-      <sheetName val="MAPPING"/>
-      <sheetName val="param"/>
-      <sheetName val="Evidence"/>
-      <sheetName val="2. 仕様差分の確認結果(for traceability)"/>
-      <sheetName val="2. 仕様差分の確認結果(for visibility)"/>
-      <sheetName val="2-1.要件分析_ストラテジ"/>
-      <sheetName val="3. 関連仕様の確認結果_詳細"/>
-      <sheetName val="設計・評価方針(仕様変化点_設計方針から抽出)"/>
-      <sheetName val="4. ソフト変更方法の詳細"/>
-      <sheetName val="ブロック図(概要)"/>
-      <sheetName val="留意点に対する設計結果_詳細"/>
-      <sheetName val="5.ソフト影響箇所の確認_詳細"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -10866,7 +11122,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -26079,7 +26335,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -26671,10 +26927,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.26953125" style="289" customWidth="1"/>
-    <col min="53" max="16384" width="8.81640625" style="289"/>
+    <col min="1" max="52" width="2.25" style="224" customWidth="1"/>
+    <col min="53" max="16384" width="8.875" style="224"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -26687,12 +26943,12 @@
     <row r="8" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="9" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="10" spans="6:20" ht="13.15" customHeight="1">
-      <c r="F10" s="290"/>
+      <c r="F10" s="225"/>
     </row>
     <row r="11" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="12" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="13" spans="6:20" ht="13.15" customHeight="1">
-      <c r="T13" s="291" t="str">
+      <c r="T13" s="226" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("[",CELL("filename",A1))+1,FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-1)</f>
         <v>alert_B_AIRBAG-CSTD-1-01-A-C0.xlsx</v>
       </c>
@@ -26716,20 +26972,20 @@
     <row r="30" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="31" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="32" spans="3:22" ht="13.15" customHeight="1">
-      <c r="C32" s="292"/>
-      <c r="V32" s="292"/>
+      <c r="C32" s="227"/>
+      <c r="V32" s="227"/>
     </row>
     <row r="33" spans="3:39" ht="13.15" customHeight="1">
-      <c r="M33" s="293"/>
-      <c r="N33" s="293"/>
-      <c r="O33" s="293"/>
-      <c r="P33" s="293"/>
-      <c r="Q33" s="293"/>
-      <c r="AF33" s="293"/>
-      <c r="AG33" s="293"/>
-      <c r="AH33" s="293"/>
-      <c r="AI33" s="293"/>
-      <c r="AJ33" s="293"/>
+      <c r="M33" s="228"/>
+      <c r="N33" s="228"/>
+      <c r="O33" s="228"/>
+      <c r="P33" s="228"/>
+      <c r="Q33" s="228"/>
+      <c r="AF33" s="228"/>
+      <c r="AG33" s="228"/>
+      <c r="AH33" s="228"/>
+      <c r="AI33" s="228"/>
+      <c r="AJ33" s="228"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="144" t="s">
@@ -26737,354 +26993,354 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="294" t="s">
+      <c r="Y35" s="250" t="s">
         <v>297</v>
       </c>
-      <c r="Z35" s="295"/>
-      <c r="AA35" s="295"/>
-      <c r="AB35" s="295"/>
-      <c r="AC35" s="296"/>
-      <c r="AD35" s="294" t="s">
+      <c r="Z35" s="251"/>
+      <c r="AA35" s="251"/>
+      <c r="AB35" s="251"/>
+      <c r="AC35" s="252"/>
+      <c r="AD35" s="250" t="s">
         <v>298</v>
       </c>
-      <c r="AE35" s="295"/>
-      <c r="AF35" s="295"/>
-      <c r="AG35" s="295"/>
-      <c r="AH35" s="296"/>
-      <c r="AI35" s="294" t="s">
+      <c r="AE35" s="251"/>
+      <c r="AF35" s="251"/>
+      <c r="AG35" s="251"/>
+      <c r="AH35" s="252"/>
+      <c r="AI35" s="250" t="s">
         <v>299</v>
       </c>
-      <c r="AJ35" s="295"/>
-      <c r="AK35" s="295"/>
-      <c r="AL35" s="295"/>
-      <c r="AM35" s="296"/>
+      <c r="AJ35" s="251"/>
+      <c r="AK35" s="251"/>
+      <c r="AL35" s="251"/>
+      <c r="AM35" s="252"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D36" s="293"/>
-      <c r="E36" s="297"/>
-      <c r="F36" s="293"/>
-      <c r="G36" s="293"/>
-      <c r="I36" s="293"/>
-      <c r="J36" s="297"/>
-      <c r="K36" s="293"/>
-      <c r="L36" s="293"/>
-      <c r="M36" s="293"/>
-      <c r="N36" s="293"/>
-      <c r="O36" s="297"/>
-      <c r="P36" s="293"/>
-      <c r="Q36" s="293"/>
-      <c r="W36" s="293"/>
-      <c r="X36" s="297"/>
-      <c r="Y36" s="298"/>
-      <c r="Z36" s="299"/>
-      <c r="AA36" s="299"/>
-      <c r="AB36" s="299"/>
-      <c r="AC36" s="300"/>
-      <c r="AD36" s="298"/>
-      <c r="AE36" s="299"/>
-      <c r="AF36" s="299"/>
-      <c r="AG36" s="299"/>
-      <c r="AH36" s="300"/>
-      <c r="AI36" s="298"/>
-      <c r="AJ36" s="299"/>
-      <c r="AK36" s="299"/>
-      <c r="AL36" s="299"/>
-      <c r="AM36" s="300"/>
+      <c r="D36" s="228"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="228"/>
+      <c r="G36" s="228"/>
+      <c r="I36" s="228"/>
+      <c r="J36" s="229"/>
+      <c r="K36" s="228"/>
+      <c r="L36" s="228"/>
+      <c r="M36" s="228"/>
+      <c r="N36" s="228"/>
+      <c r="O36" s="229"/>
+      <c r="P36" s="228"/>
+      <c r="Q36" s="228"/>
+      <c r="W36" s="228"/>
+      <c r="X36" s="229"/>
+      <c r="Y36" s="230"/>
+      <c r="Z36" s="231"/>
+      <c r="AA36" s="231"/>
+      <c r="AB36" s="231"/>
+      <c r="AC36" s="232"/>
+      <c r="AD36" s="230"/>
+      <c r="AE36" s="231"/>
+      <c r="AF36" s="231"/>
+      <c r="AG36" s="231"/>
+      <c r="AH36" s="232"/>
+      <c r="AI36" s="230"/>
+      <c r="AJ36" s="231"/>
+      <c r="AK36" s="231"/>
+      <c r="AL36" s="231"/>
+      <c r="AM36" s="232"/>
     </row>
     <row r="37" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y37" s="301"/>
-      <c r="AC37" s="302"/>
-      <c r="AD37" s="301"/>
-      <c r="AH37" s="302"/>
-      <c r="AI37" s="301"/>
-      <c r="AM37" s="302"/>
+      <c r="Y37" s="233"/>
+      <c r="AC37" s="234"/>
+      <c r="AD37" s="233"/>
+      <c r="AH37" s="234"/>
+      <c r="AI37" s="233"/>
+      <c r="AM37" s="234"/>
     </row>
     <row r="38" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y38" s="301"/>
-      <c r="Z38" s="293"/>
-      <c r="AA38" s="297" t="s">
+      <c r="Y38" s="233"/>
+      <c r="Z38" s="228"/>
+      <c r="AA38" s="229" t="s">
         <v>300</v>
       </c>
-      <c r="AB38" s="293"/>
-      <c r="AC38" s="303"/>
-      <c r="AD38" s="301"/>
-      <c r="AE38" s="293"/>
-      <c r="AF38" s="297" t="s">
+      <c r="AB38" s="228"/>
+      <c r="AC38" s="235"/>
+      <c r="AD38" s="233"/>
+      <c r="AE38" s="228"/>
+      <c r="AF38" s="229" t="s">
         <v>301</v>
       </c>
-      <c r="AG38" s="293"/>
-      <c r="AH38" s="303"/>
-      <c r="AI38" s="304"/>
-      <c r="AJ38" s="293"/>
-      <c r="AK38" s="297" t="s">
+      <c r="AG38" s="228"/>
+      <c r="AH38" s="235"/>
+      <c r="AI38" s="236"/>
+      <c r="AJ38" s="228"/>
+      <c r="AK38" s="229" t="s">
         <v>302</v>
       </c>
-      <c r="AL38" s="293"/>
-      <c r="AM38" s="303"/>
+      <c r="AL38" s="228"/>
+      <c r="AM38" s="235"/>
     </row>
     <row r="39" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y39" s="301"/>
-      <c r="AC39" s="302"/>
-      <c r="AD39" s="301"/>
-      <c r="AH39" s="302"/>
-      <c r="AI39" s="301"/>
-      <c r="AM39" s="302"/>
+      <c r="Y39" s="233"/>
+      <c r="AC39" s="234"/>
+      <c r="AD39" s="233"/>
+      <c r="AH39" s="234"/>
+      <c r="AI39" s="233"/>
+      <c r="AM39" s="234"/>
     </row>
     <row r="40" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C40" s="292"/>
-      <c r="V40" s="292"/>
-      <c r="Y40" s="305"/>
-      <c r="Z40" s="306"/>
-      <c r="AA40" s="306"/>
-      <c r="AB40" s="306"/>
-      <c r="AC40" s="307"/>
-      <c r="AD40" s="305"/>
-      <c r="AE40" s="306"/>
-      <c r="AF40" s="306"/>
-      <c r="AG40" s="306"/>
-      <c r="AH40" s="307"/>
-      <c r="AI40" s="305"/>
-      <c r="AJ40" s="306"/>
-      <c r="AK40" s="306"/>
-      <c r="AL40" s="306"/>
-      <c r="AM40" s="307"/>
+      <c r="C40" s="227"/>
+      <c r="V40" s="227"/>
+      <c r="Y40" s="237"/>
+      <c r="Z40" s="238"/>
+      <c r="AA40" s="238"/>
+      <c r="AB40" s="238"/>
+      <c r="AC40" s="239"/>
+      <c r="AD40" s="237"/>
+      <c r="AE40" s="238"/>
+      <c r="AF40" s="238"/>
+      <c r="AG40" s="238"/>
+      <c r="AH40" s="239"/>
+      <c r="AI40" s="237"/>
+      <c r="AJ40" s="238"/>
+      <c r="AK40" s="238"/>
+      <c r="AL40" s="238"/>
+      <c r="AM40" s="239"/>
     </row>
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y42" s="292" t="s">
+      <c r="Y42" s="227" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="294" t="s">
+      <c r="Y43" s="250" t="s">
         <v>297</v>
       </c>
-      <c r="Z43" s="295"/>
-      <c r="AA43" s="295"/>
-      <c r="AB43" s="295"/>
-      <c r="AC43" s="296"/>
-      <c r="AD43" s="294" t="s">
+      <c r="Z43" s="251"/>
+      <c r="AA43" s="251"/>
+      <c r="AB43" s="251"/>
+      <c r="AC43" s="252"/>
+      <c r="AD43" s="250" t="s">
         <v>298</v>
       </c>
-      <c r="AE43" s="295"/>
-      <c r="AF43" s="295"/>
-      <c r="AG43" s="295"/>
-      <c r="AH43" s="296"/>
-      <c r="AI43" s="294" t="s">
+      <c r="AE43" s="251"/>
+      <c r="AF43" s="251"/>
+      <c r="AG43" s="251"/>
+      <c r="AH43" s="252"/>
+      <c r="AI43" s="250" t="s">
         <v>299</v>
       </c>
-      <c r="AJ43" s="295"/>
-      <c r="AK43" s="295"/>
-      <c r="AL43" s="295"/>
-      <c r="AM43" s="296"/>
+      <c r="AJ43" s="251"/>
+      <c r="AK43" s="251"/>
+      <c r="AL43" s="251"/>
+      <c r="AM43" s="252"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D44" s="293"/>
-      <c r="E44" s="297"/>
-      <c r="F44" s="293"/>
-      <c r="G44" s="293"/>
-      <c r="H44" s="293"/>
-      <c r="I44" s="293"/>
-      <c r="J44" s="297"/>
-      <c r="K44" s="293"/>
-      <c r="L44" s="293"/>
-      <c r="M44" s="293"/>
-      <c r="N44" s="293"/>
-      <c r="O44" s="297"/>
-      <c r="P44" s="293"/>
-      <c r="Q44" s="293"/>
-      <c r="W44" s="293"/>
-      <c r="X44" s="297"/>
-      <c r="Y44" s="298"/>
-      <c r="Z44" s="299"/>
-      <c r="AA44" s="299"/>
-      <c r="AB44" s="299"/>
-      <c r="AC44" s="300"/>
-      <c r="AD44" s="299"/>
-      <c r="AE44" s="299"/>
-      <c r="AF44" s="299"/>
-      <c r="AG44" s="299"/>
-      <c r="AH44" s="300"/>
-      <c r="AI44" s="298"/>
-      <c r="AJ44" s="299"/>
-      <c r="AK44" s="299"/>
-      <c r="AL44" s="299"/>
-      <c r="AM44" s="300"/>
+      <c r="D44" s="228"/>
+      <c r="E44" s="229"/>
+      <c r="F44" s="228"/>
+      <c r="G44" s="228"/>
+      <c r="H44" s="228"/>
+      <c r="I44" s="228"/>
+      <c r="J44" s="229"/>
+      <c r="K44" s="228"/>
+      <c r="L44" s="228"/>
+      <c r="M44" s="228"/>
+      <c r="N44" s="228"/>
+      <c r="O44" s="229"/>
+      <c r="P44" s="228"/>
+      <c r="Q44" s="228"/>
+      <c r="W44" s="228"/>
+      <c r="X44" s="229"/>
+      <c r="Y44" s="230"/>
+      <c r="Z44" s="231"/>
+      <c r="AA44" s="231"/>
+      <c r="AB44" s="231"/>
+      <c r="AC44" s="232"/>
+      <c r="AD44" s="231"/>
+      <c r="AE44" s="231"/>
+      <c r="AF44" s="231"/>
+      <c r="AG44" s="231"/>
+      <c r="AH44" s="232"/>
+      <c r="AI44" s="230"/>
+      <c r="AJ44" s="231"/>
+      <c r="AK44" s="231"/>
+      <c r="AL44" s="231"/>
+      <c r="AM44" s="232"/>
     </row>
     <row r="45" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y45" s="301"/>
-      <c r="AC45" s="302"/>
-      <c r="AH45" s="302"/>
-      <c r="AI45" s="301"/>
-      <c r="AM45" s="302"/>
+      <c r="Y45" s="233"/>
+      <c r="AC45" s="234"/>
+      <c r="AH45" s="234"/>
+      <c r="AI45" s="233"/>
+      <c r="AM45" s="234"/>
     </row>
     <row r="46" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y46" s="301"/>
-      <c r="Z46" s="293"/>
-      <c r="AA46" s="297" t="s">
+      <c r="Y46" s="233"/>
+      <c r="Z46" s="228"/>
+      <c r="AA46" s="229" t="s">
         <v>304</v>
       </c>
-      <c r="AB46" s="293"/>
-      <c r="AC46" s="303"/>
-      <c r="AD46" s="293"/>
-      <c r="AE46" s="293"/>
-      <c r="AF46" s="297" t="s">
+      <c r="AB46" s="228"/>
+      <c r="AC46" s="235"/>
+      <c r="AD46" s="228"/>
+      <c r="AE46" s="228"/>
+      <c r="AF46" s="229" t="s">
         <v>305</v>
       </c>
-      <c r="AG46" s="293"/>
-      <c r="AH46" s="303"/>
-      <c r="AI46" s="304"/>
-      <c r="AJ46" s="293"/>
-      <c r="AK46" s="297" t="s">
+      <c r="AG46" s="228"/>
+      <c r="AH46" s="235"/>
+      <c r="AI46" s="236"/>
+      <c r="AJ46" s="228"/>
+      <c r="AK46" s="229" t="s">
         <v>306</v>
       </c>
-      <c r="AL46" s="293"/>
-      <c r="AM46" s="303"/>
+      <c r="AL46" s="228"/>
+      <c r="AM46" s="235"/>
     </row>
     <row r="47" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y47" s="301"/>
-      <c r="AC47" s="302"/>
-      <c r="AH47" s="302"/>
-      <c r="AI47" s="301"/>
-      <c r="AM47" s="302"/>
+      <c r="Y47" s="233"/>
+      <c r="AC47" s="234"/>
+      <c r="AH47" s="234"/>
+      <c r="AI47" s="233"/>
+      <c r="AM47" s="234"/>
     </row>
     <row r="48" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C48" s="292"/>
-      <c r="V48" s="292"/>
-      <c r="Y48" s="305"/>
-      <c r="Z48" s="306"/>
-      <c r="AA48" s="306"/>
-      <c r="AB48" s="306"/>
-      <c r="AC48" s="307"/>
-      <c r="AD48" s="306"/>
-      <c r="AE48" s="306"/>
-      <c r="AF48" s="306"/>
-      <c r="AG48" s="306"/>
-      <c r="AH48" s="307"/>
-      <c r="AI48" s="305"/>
-      <c r="AJ48" s="306"/>
-      <c r="AK48" s="306"/>
-      <c r="AL48" s="306"/>
-      <c r="AM48" s="307"/>
+      <c r="C48" s="227"/>
+      <c r="V48" s="227"/>
+      <c r="Y48" s="237"/>
+      <c r="Z48" s="238"/>
+      <c r="AA48" s="238"/>
+      <c r="AB48" s="238"/>
+      <c r="AC48" s="239"/>
+      <c r="AD48" s="238"/>
+      <c r="AE48" s="238"/>
+      <c r="AF48" s="238"/>
+      <c r="AG48" s="238"/>
+      <c r="AH48" s="239"/>
+      <c r="AI48" s="237"/>
+      <c r="AJ48" s="238"/>
+      <c r="AK48" s="238"/>
+      <c r="AL48" s="238"/>
+      <c r="AM48" s="239"/>
     </row>
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y50" s="292" t="s">
+      <c r="Y50" s="227" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="294" t="s">
+      <c r="Y51" s="250" t="s">
         <v>297</v>
       </c>
-      <c r="Z51" s="295"/>
-      <c r="AA51" s="295"/>
-      <c r="AB51" s="295"/>
-      <c r="AC51" s="296"/>
-      <c r="AD51" s="294" t="s">
+      <c r="Z51" s="251"/>
+      <c r="AA51" s="251"/>
+      <c r="AB51" s="251"/>
+      <c r="AC51" s="252"/>
+      <c r="AD51" s="250" t="s">
         <v>298</v>
       </c>
-      <c r="AE51" s="295"/>
-      <c r="AF51" s="295"/>
-      <c r="AG51" s="295"/>
-      <c r="AH51" s="296"/>
-      <c r="AI51" s="294" t="s">
+      <c r="AE51" s="251"/>
+      <c r="AF51" s="251"/>
+      <c r="AG51" s="251"/>
+      <c r="AH51" s="252"/>
+      <c r="AI51" s="250" t="s">
         <v>299</v>
       </c>
-      <c r="AJ51" s="295"/>
-      <c r="AK51" s="295"/>
-      <c r="AL51" s="295"/>
-      <c r="AM51" s="296"/>
+      <c r="AJ51" s="251"/>
+      <c r="AK51" s="251"/>
+      <c r="AL51" s="251"/>
+      <c r="AM51" s="252"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
-      <c r="D52" s="293"/>
-      <c r="E52" s="297"/>
-      <c r="F52" s="293"/>
-      <c r="G52" s="293"/>
-      <c r="H52" s="293"/>
-      <c r="I52" s="293"/>
-      <c r="J52" s="297"/>
-      <c r="K52" s="293"/>
-      <c r="L52" s="293"/>
-      <c r="M52" s="293"/>
-      <c r="N52" s="293"/>
-      <c r="O52" s="297"/>
-      <c r="P52" s="293"/>
-      <c r="Q52" s="293"/>
-      <c r="W52" s="293"/>
-      <c r="X52" s="297"/>
-      <c r="Y52" s="298"/>
-      <c r="Z52" s="299"/>
-      <c r="AA52" s="299"/>
-      <c r="AB52" s="299"/>
-      <c r="AC52" s="300"/>
-      <c r="AD52" s="299"/>
-      <c r="AE52" s="299"/>
-      <c r="AF52" s="299"/>
-      <c r="AG52" s="299"/>
-      <c r="AH52" s="300"/>
-      <c r="AI52" s="298"/>
-      <c r="AJ52" s="299"/>
-      <c r="AK52" s="299"/>
-      <c r="AL52" s="299"/>
-      <c r="AM52" s="300"/>
+      <c r="D52" s="228"/>
+      <c r="E52" s="229"/>
+      <c r="F52" s="228"/>
+      <c r="G52" s="228"/>
+      <c r="H52" s="228"/>
+      <c r="I52" s="228"/>
+      <c r="J52" s="229"/>
+      <c r="K52" s="228"/>
+      <c r="L52" s="228"/>
+      <c r="M52" s="228"/>
+      <c r="N52" s="228"/>
+      <c r="O52" s="229"/>
+      <c r="P52" s="228"/>
+      <c r="Q52" s="228"/>
+      <c r="W52" s="228"/>
+      <c r="X52" s="229"/>
+      <c r="Y52" s="230"/>
+      <c r="Z52" s="231"/>
+      <c r="AA52" s="231"/>
+      <c r="AB52" s="231"/>
+      <c r="AC52" s="232"/>
+      <c r="AD52" s="231"/>
+      <c r="AE52" s="231"/>
+      <c r="AF52" s="231"/>
+      <c r="AG52" s="231"/>
+      <c r="AH52" s="232"/>
+      <c r="AI52" s="230"/>
+      <c r="AJ52" s="231"/>
+      <c r="AK52" s="231"/>
+      <c r="AL52" s="231"/>
+      <c r="AM52" s="232"/>
     </row>
     <row r="53" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y53" s="301"/>
-      <c r="AC53" s="302"/>
-      <c r="AH53" s="302"/>
-      <c r="AI53" s="301"/>
-      <c r="AM53" s="302"/>
+      <c r="Y53" s="233"/>
+      <c r="AC53" s="234"/>
+      <c r="AH53" s="234"/>
+      <c r="AI53" s="233"/>
+      <c r="AM53" s="234"/>
     </row>
     <row r="54" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y54" s="301"/>
-      <c r="Z54" s="293"/>
-      <c r="AA54" s="297" t="s">
+      <c r="Y54" s="233"/>
+      <c r="Z54" s="228"/>
+      <c r="AA54" s="229" t="s">
         <v>308</v>
       </c>
-      <c r="AB54" s="293"/>
-      <c r="AC54" s="303"/>
-      <c r="AD54" s="293"/>
-      <c r="AE54" s="293"/>
-      <c r="AF54" s="297" t="s">
+      <c r="AB54" s="228"/>
+      <c r="AC54" s="235"/>
+      <c r="AD54" s="228"/>
+      <c r="AE54" s="228"/>
+      <c r="AF54" s="229" t="s">
         <v>309</v>
       </c>
-      <c r="AG54" s="293"/>
-      <c r="AH54" s="303"/>
-      <c r="AI54" s="304"/>
-      <c r="AJ54" s="293"/>
-      <c r="AK54" s="297" t="s">
+      <c r="AG54" s="228"/>
+      <c r="AH54" s="235"/>
+      <c r="AI54" s="236"/>
+      <c r="AJ54" s="228"/>
+      <c r="AK54" s="229" t="s">
         <v>302</v>
       </c>
-      <c r="AL54" s="293"/>
-      <c r="AM54" s="303"/>
+      <c r="AL54" s="228"/>
+      <c r="AM54" s="235"/>
     </row>
     <row r="55" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y55" s="301"/>
-      <c r="AC55" s="302"/>
-      <c r="AH55" s="302"/>
-      <c r="AI55" s="301"/>
-      <c r="AM55" s="302"/>
+      <c r="Y55" s="233"/>
+      <c r="AC55" s="234"/>
+      <c r="AH55" s="234"/>
+      <c r="AI55" s="233"/>
+      <c r="AM55" s="234"/>
     </row>
     <row r="56" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y56" s="305"/>
-      <c r="Z56" s="306"/>
-      <c r="AA56" s="306"/>
-      <c r="AB56" s="306"/>
-      <c r="AC56" s="307"/>
-      <c r="AD56" s="306"/>
-      <c r="AE56" s="306"/>
-      <c r="AF56" s="306"/>
-      <c r="AG56" s="306"/>
-      <c r="AH56" s="307"/>
-      <c r="AI56" s="305"/>
-      <c r="AJ56" s="306"/>
-      <c r="AK56" s="306"/>
-      <c r="AL56" s="306"/>
-      <c r="AM56" s="307"/>
+      <c r="Y56" s="237"/>
+      <c r="Z56" s="238"/>
+      <c r="AA56" s="238"/>
+      <c r="AB56" s="238"/>
+      <c r="AC56" s="239"/>
+      <c r="AD56" s="238"/>
+      <c r="AE56" s="238"/>
+      <c r="AF56" s="238"/>
+      <c r="AG56" s="238"/>
+      <c r="AH56" s="239"/>
+      <c r="AI56" s="237"/>
+      <c r="AJ56" s="238"/>
+      <c r="AK56" s="238"/>
+      <c r="AL56" s="238"/>
+      <c r="AM56" s="239"/>
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
-      <c r="AK57" s="289" t="s">
+      <c r="AK57" s="224" t="s">
         <v>310</v>
       </c>
     </row>
@@ -27110,20 +27366,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="B2:X14"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.453125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="13" hidden="1" customWidth="1"/>
-    <col min="20" max="20" width="10.7265625" hidden="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="12" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="10.90625" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="12.453125" customWidth="1"/>
-    <col min="24" max="24" width="12.36328125" customWidth="1"/>
+    <col min="22" max="22" width="10.875" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="12.5" customWidth="1"/>
+    <col min="24" max="24" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -27134,18 +27390,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="229" t="s">
+      <c r="I2" s="253" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="229"/>
-      <c r="K2" s="229"/>
-      <c r="L2" s="229"/>
-      <c r="M2" s="229"/>
-      <c r="N2" s="229"/>
-      <c r="O2" s="229"/>
-      <c r="P2" s="229"/>
-      <c r="Q2" s="229"/>
-      <c r="R2" s="229"/>
+      <c r="J2" s="253"/>
+      <c r="K2" s="253"/>
+      <c r="L2" s="253"/>
+      <c r="M2" s="253"/>
+      <c r="N2" s="253"/>
+      <c r="O2" s="253"/>
+      <c r="P2" s="253"/>
+      <c r="Q2" s="253"/>
+      <c r="R2" s="253"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -27158,24 +27414,24 @@
       <c r="H3" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="I3" s="230" t="s">
+      <c r="I3" s="254" t="s">
         <v>196</v>
       </c>
-      <c r="J3" s="231"/>
-      <c r="K3" s="231"/>
-      <c r="L3" s="231"/>
-      <c r="M3" s="231"/>
-      <c r="N3" s="231"/>
-      <c r="O3" s="231"/>
-      <c r="P3" s="231"/>
-      <c r="Q3" s="231"/>
-      <c r="R3" s="231"/>
+      <c r="J3" s="255"/>
+      <c r="K3" s="255"/>
+      <c r="L3" s="255"/>
+      <c r="M3" s="255"/>
+      <c r="N3" s="255"/>
+      <c r="O3" s="255"/>
+      <c r="P3" s="255"/>
+      <c r="Q3" s="255"/>
+      <c r="R3" s="255"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="22" t="str">
-        <f>DGET(B8:C14,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
         <v>1.2.1</v>
       </c>
       <c r="F4" s="6"/>
@@ -27189,46 +27445,46 @@
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
       <c r="H5" s="11">
-        <f>MAX(B9:B14)</f>
+        <f>MAX(B9:B15)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:24">
-      <c r="C7" s="235" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="236"/>
-      <c r="E7" s="237" t="s">
+      <c r="C7" s="259" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="260"/>
+      <c r="E7" s="261" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="237"/>
-      <c r="G7" s="238" t="s">
+      <c r="F7" s="261"/>
+      <c r="G7" s="262" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="238"/>
-      <c r="I7" s="238"/>
-      <c r="J7" s="238"/>
-      <c r="K7" s="238"/>
-      <c r="L7" s="238"/>
-      <c r="M7" s="239" t="s">
+      <c r="H7" s="262"/>
+      <c r="I7" s="262"/>
+      <c r="J7" s="262"/>
+      <c r="K7" s="262"/>
+      <c r="L7" s="262"/>
+      <c r="M7" s="263" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="239"/>
-      <c r="O7" s="239"/>
-      <c r="P7" s="239"/>
-      <c r="Q7" s="239"/>
-      <c r="R7" s="239"/>
-      <c r="S7" s="232" t="s">
+      <c r="N7" s="263"/>
+      <c r="O7" s="263"/>
+      <c r="P7" s="263"/>
+      <c r="Q7" s="263"/>
+      <c r="R7" s="263"/>
+      <c r="S7" s="256" t="s">
         <v>291</v>
       </c>
-      <c r="T7" s="233"/>
-      <c r="U7" s="233"/>
-      <c r="V7" s="233"/>
-      <c r="W7" s="233"/>
-      <c r="X7" s="234"/>
+      <c r="T7" s="257"/>
+      <c r="U7" s="257"/>
+      <c r="V7" s="257"/>
+      <c r="W7" s="257"/>
+      <c r="X7" s="258"/>
     </row>
-    <row r="8" spans="2:24" ht="26.5" thickBot="1">
+    <row r="8" spans="2:24" ht="27.75" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>92</v>
       </c>
@@ -27299,7 +27555,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="13.5" thickTop="1">
+    <row r="9" spans="2:24" ht="14.25" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -27371,9 +27627,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="78">
+    <row r="10" spans="2:24" ht="81">
       <c r="B10" s="9">
-        <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -27435,7 +27691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="2:24" ht="39">
+    <row r="11" spans="2:24" ht="40.5">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -27507,73 +27763,101 @@
         <v>45975</v>
       </c>
     </row>
-    <row r="12" spans="2:24" ht="78">
+    <row r="12" spans="2:24" ht="81">
       <c r="B12" s="9">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C12" s="224" t="s">
+      <c r="C12" s="240" t="s">
         <v>294</v>
       </c>
-      <c r="D12" s="225" t="s">
+      <c r="D12" s="241" t="s">
         <v>295</v>
       </c>
-      <c r="E12" s="226" t="s">
+      <c r="E12" s="242" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="226" t="s">
+      <c r="F12" s="242" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="220"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
-      <c r="V12" s="1"/>
-      <c r="W12" s="227" t="s">
+      <c r="G12" s="243"/>
+      <c r="H12" s="243"/>
+      <c r="I12" s="243"/>
+      <c r="J12" s="243"/>
+      <c r="K12" s="243"/>
+      <c r="L12" s="243"/>
+      <c r="M12" s="243"/>
+      <c r="N12" s="243"/>
+      <c r="O12" s="243"/>
+      <c r="P12" s="243"/>
+      <c r="Q12" s="243"/>
+      <c r="R12" s="243"/>
+      <c r="S12" s="244"/>
+      <c r="T12" s="243"/>
+      <c r="U12" s="243"/>
+      <c r="V12" s="243"/>
+      <c r="W12" s="243" t="s">
         <v>293</v>
       </c>
-      <c r="X12" s="228">
+      <c r="X12" s="246">
         <v>46008</v>
       </c>
     </row>
-    <row r="13" spans="2:24" ht="13.5" thickBot="1">
-      <c r="B13" s="9">
+    <row r="13" spans="2:24" ht="40.5">
+      <c r="C13" s="248" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="249" t="s">
+        <v>312</v>
+      </c>
+      <c r="E13" s="242"/>
+      <c r="F13" s="242"/>
+      <c r="G13" s="242"/>
+      <c r="H13" s="242"/>
+      <c r="I13" s="242"/>
+      <c r="J13" s="242"/>
+      <c r="K13" s="242"/>
+      <c r="L13" s="242"/>
+      <c r="M13" s="242"/>
+      <c r="N13" s="242"/>
+      <c r="O13" s="242"/>
+      <c r="P13" s="242"/>
+      <c r="Q13" s="242"/>
+      <c r="R13" s="242"/>
+      <c r="S13" s="247"/>
+      <c r="T13" s="242"/>
+      <c r="U13" s="242"/>
+      <c r="V13" s="242"/>
+      <c r="W13" s="245"/>
+      <c r="X13" s="246"/>
+    </row>
+    <row r="14" spans="2:24" ht="14.25" thickBot="1">
+      <c r="B14" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="221"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="5"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4"/>
+      <c r="Q14" s="4"/>
+      <c r="R14" s="4"/>
+      <c r="S14" s="221"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4"/>
+      <c r="V14" s="4"/>
+      <c r="W14" s="4"/>
+      <c r="X14" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -27601,11 +27885,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -27619,13 +27903,13 @@
         <v>138</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="144" t="s">
         <v>129</v>
       </c>
       <c r="C6" s="144"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="72" t="s">
         <v>131</v>
       </c>
@@ -27645,7 +27929,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="154">
         <v>1</v>
       </c>
@@ -27656,7 +27940,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="152"/>
       <c r="D10" s="83"/>
       <c r="E10" s="5"/>
@@ -27664,14 +27948,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="150"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="145" t="s">
         <v>130</v>
       </c>
       <c r="C12" s="79"/>
       <c r="D12" s="79"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="146"/>
       <c r="C13" s="151" t="s">
         <v>131</v>
@@ -27683,7 +27967,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="148">
         <v>0</v>
       </c>
@@ -27760,17 +28044,17 @@
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="152"/>
       <c r="D21" s="83"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="144" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="151" t="s">
         <v>131</v>
       </c>
@@ -27792,7 +28076,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120.25" customHeight="1">
+    <row r="27" spans="2:5" ht="120.2" customHeight="1">
       <c r="C27" s="149">
         <v>1</v>
       </c>
@@ -27857,26 +28141,26 @@
       <c r="D33" s="82"/>
       <c r="E33" s="68"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="152"/>
       <c r="D34" s="83"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="144" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="240"/>
-      <c r="D38" s="241"/>
+      <c r="C38" s="264"/>
+      <c r="D38" s="265"/>
       <c r="E38" s="108" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="242"/>
-      <c r="D39" s="243"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="266"/>
+      <c r="D39" s="267"/>
       <c r="E39" s="5" t="s">
         <v>119</v>
       </c>
@@ -27905,133 +28189,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="269" t="s">
+      <c r="B2" s="268" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="270"/>
-      <c r="D2" s="257" t="s">
+      <c r="C2" s="269"/>
+      <c r="D2" s="274" t="s">
         <v>280</v>
       </c>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
-      <c r="G2" s="258"/>
-      <c r="H2" s="259"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="276"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="244" t="s">
+      <c r="B3" s="270" t="s">
         <v>116</v>
       </c>
-      <c r="C3" s="245"/>
-      <c r="D3" s="260" t="s">
+      <c r="C3" s="271"/>
+      <c r="D3" s="277" t="s">
         <v>281</v>
       </c>
-      <c r="E3" s="261"/>
-      <c r="F3" s="261"/>
-      <c r="G3" s="261"/>
-      <c r="H3" s="262"/>
+      <c r="E3" s="278"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
+      <c r="H3" s="279"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="255" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="272" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="256"/>
-      <c r="D4" s="263" t="str">
+      <c r="C4" s="273"/>
+      <c r="D4" s="280" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_B_AIRBAG-CSTD-1-01-A-C0.c</v>
       </c>
-      <c r="E4" s="264"/>
-      <c r="F4" s="264"/>
-      <c r="G4" s="264"/>
-      <c r="H4" s="265"/>
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="269" t="s">
+      <c r="B6" s="268" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="270"/>
-      <c r="D6" s="266" t="str">
+      <c r="C6" s="269"/>
+      <c r="D6" s="283" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>B_AIRBAG</v>
       </c>
-      <c r="E6" s="267"/>
-      <c r="F6" s="267"/>
-      <c r="G6" s="267"/>
-      <c r="H6" s="268"/>
+      <c r="E6" s="284"/>
+      <c r="F6" s="284"/>
+      <c r="G6" s="284"/>
+      <c r="H6" s="285"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="244" t="s">
+      <c r="B7" s="270" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="245"/>
-      <c r="D7" s="246">
+      <c r="C7" s="271"/>
+      <c r="D7" s="286">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="247"/>
-      <c r="F7" s="247"/>
-      <c r="G7" s="247"/>
-      <c r="H7" s="248"/>
+      <c r="E7" s="287"/>
+      <c r="F7" s="287"/>
+      <c r="G7" s="287"/>
+      <c r="H7" s="288"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="244" t="s">
+      <c r="B8" s="270" t="s">
         <v>95</v>
       </c>
-      <c r="C8" s="245"/>
-      <c r="D8" s="246" t="str">
+      <c r="C8" s="271"/>
+      <c r="D8" s="286" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_B_AIRBAG_MTRX</v>
       </c>
-      <c r="E8" s="247"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="248"/>
+      <c r="E8" s="287"/>
+      <c r="F8" s="287"/>
+      <c r="G8" s="287"/>
+      <c r="H8" s="288"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="244" t="s">
+      <c r="B9" s="270" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="245"/>
-      <c r="D9" s="249" t="s">
+      <c r="C9" s="271"/>
+      <c r="D9" s="289" t="s">
         <v>287</v>
       </c>
-      <c r="E9" s="250"/>
-      <c r="F9" s="250"/>
-      <c r="G9" s="250"/>
-      <c r="H9" s="251"/>
+      <c r="E9" s="290"/>
+      <c r="F9" s="290"/>
+      <c r="G9" s="290"/>
+      <c r="H9" s="291"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="255" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="272" t="s">
         <v>44</v>
       </c>
-      <c r="C10" s="256"/>
-      <c r="D10" s="252">
+      <c r="C10" s="273"/>
+      <c r="D10" s="292">
         <v>87</v>
       </c>
-      <c r="E10" s="253"/>
-      <c r="F10" s="253"/>
-      <c r="G10" s="253"/>
-      <c r="H10" s="254"/>
+      <c r="E10" s="293"/>
+      <c r="F10" s="293"/>
+      <c r="G10" s="293"/>
+      <c r="H10" s="294"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="135" t="s">
         <v>34</v>
       </c>
@@ -28066,7 +28350,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="101">
         <v>1</v>
       </c>
@@ -28919,7 +29203,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="92">
         <v>25</v>
       </c>
@@ -28960,22 +29244,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -29022,21 +29306,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>188</v>
       </c>
@@ -29044,7 +29328,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="135" t="s">
         <v>34</v>
       </c>
@@ -29082,7 +29366,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="165">
         <v>0</v>
       </c>
@@ -29110,7 +29394,7 @@
       </c>
       <c r="R4" s="134"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="168">
         <v>1</v>
       </c>
@@ -29638,7 +29922,7 @@
       <c r="Q28" s="139"/>
       <c r="R28" s="111"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="169">
         <v>25</v>
       </c>
@@ -29660,7 +29944,7 @@
       <c r="Q29" s="137"/>
       <c r="R29" s="113"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>189</v>
       </c>
@@ -29668,7 +29952,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="135" t="s">
         <v>34</v>
       </c>
@@ -29700,7 +29984,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="165">
         <v>0</v>
       </c>
@@ -29726,7 +30010,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="168">
         <v>1</v>
       </c>
@@ -30254,7 +30538,7 @@
       <c r="Q58" s="139"/>
       <c r="R58" s="170"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="169">
         <v>25</v>
       </c>
@@ -30305,29 +30589,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="28.453125" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="28.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="85" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="93" t="s">
         <v>58</v>
       </c>
@@ -30371,7 +30655,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="24"/>
       <c r="C3" s="44" t="s">
         <v>108</v>
@@ -30392,7 +30676,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="24" t="s">
         <v>205</v>
       </c>
@@ -30682,7 +30966,7 @@
       </c>
       <c r="U12" s="27"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="24"/>
       <c r="C13" s="23"/>
       <c r="D13" s="110"/>
@@ -32933,7 +33217,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="46"/>
       <c r="C103" s="47"/>
       <c r="D103" s="112"/>
@@ -33006,18 +33290,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -33033,7 +33317,7 @@
       <c r="B2" s="120" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="271" t="s">
+      <c r="C2" s="295" t="s">
         <v>84</v>
       </c>
       <c r="D2" s="51">
@@ -33132,7 +33416,7 @@
       <c r="AI2" s="51">
         <v>0</v>
       </c>
-      <c r="AJ2" s="273" t="s">
+      <c r="AJ2" s="297" t="s">
         <v>155</v>
       </c>
     </row>
@@ -33141,7 +33425,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="272"/>
+      <c r="C3" s="296"/>
       <c r="D3" s="122" t="s">
         <v>61</v>
       </c>
@@ -33226,24 +33510,24 @@
       <c r="AE3" s="123" t="s">
         <v>62</v>
       </c>
-      <c r="AF3" s="279" t="s">
+      <c r="AF3" s="303" t="s">
         <v>284</v>
       </c>
-      <c r="AG3" s="280"/>
-      <c r="AH3" s="281" t="s">
+      <c r="AG3" s="304"/>
+      <c r="AH3" s="305" t="s">
         <v>277</v>
       </c>
-      <c r="AI3" s="280"/>
-      <c r="AJ3" s="274"/>
+      <c r="AI3" s="304"/>
+      <c r="AJ3" s="298"/>
       <c r="AR3" s="86" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="275" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="299" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="276"/>
+      <c r="B4" s="300"/>
       <c r="C4" s="132"/>
       <c r="D4" s="132"/>
       <c r="E4" s="132"/>
@@ -33287,9 +33571,9 @@
       <c r="AV4" s="75"/>
       <c r="AW4" s="76"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="277"/>
-      <c r="B5" s="278"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="301"/>
+      <c r="B5" s="302"/>
       <c r="C5" s="133"/>
       <c r="D5" s="133"/>
       <c r="E5" s="133"/>
@@ -34804,7 +35088,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="129"/>
       <c r="C17" s="40">
         <f t="shared" si="2"/>
@@ -41184,7 +41468,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="49" t="s">
         <v>64</v>
       </c>
@@ -61816,19 +62100,19 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AZ226"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="42" bestFit="1" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="30.453125" customWidth="1"/>
+    <col min="12" max="12" width="30.5" customWidth="1"/>
     <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
-    <col min="16" max="17" width="10.90625" customWidth="1"/>
+    <col min="16" max="17" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:52" ht="14.5" thickBot="1">
+    <row r="2" spans="2:52" ht="15" thickBot="1">
       <c r="B2" s="25" t="s">
         <v>211</v>
       </c>
@@ -61866,20 +62150,20 @@
       <c r="AY2" s="181"/>
       <c r="AZ2" s="181"/>
     </row>
-    <row r="3" spans="2:52" ht="14.5" thickBot="1">
+    <row r="3" spans="2:52" ht="15" thickBot="1">
       <c r="B3" s="90" t="s">
         <v>212</v>
       </c>
-      <c r="C3" s="286" t="s">
+      <c r="C3" s="310" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="287"/>
-      <c r="E3" s="287"/>
-      <c r="F3" s="287"/>
-      <c r="G3" s="287"/>
-      <c r="H3" s="287"/>
-      <c r="I3" s="287"/>
-      <c r="J3" s="288"/>
+      <c r="D3" s="311"/>
+      <c r="E3" s="311"/>
+      <c r="F3" s="311"/>
+      <c r="G3" s="311"/>
+      <c r="H3" s="311"/>
+      <c r="I3" s="311"/>
+      <c r="J3" s="312"/>
       <c r="K3" s="161"/>
       <c r="L3" s="161"/>
       <c r="M3" s="164"/>
@@ -61916,16 +62200,16 @@
       <c r="B5" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="282" t="s">
+      <c r="C5" s="306" t="s">
         <v>215</v>
       </c>
-      <c r="D5" s="283"/>
-      <c r="E5" s="283"/>
-      <c r="F5" s="283"/>
-      <c r="G5" s="283"/>
-      <c r="H5" s="283"/>
-      <c r="I5" s="283"/>
-      <c r="J5" s="284"/>
+      <c r="D5" s="307"/>
+      <c r="E5" s="307"/>
+      <c r="F5" s="307"/>
+      <c r="G5" s="307"/>
+      <c r="H5" s="307"/>
+      <c r="I5" s="307"/>
+      <c r="J5" s="308"/>
       <c r="K5" s="186" t="s">
         <v>216</v>
       </c>
@@ -61946,7 +62230,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="6" spans="2:52" ht="26">
+    <row r="6" spans="2:52" ht="27">
       <c r="B6" s="64" t="s">
         <v>33</v>
       </c>
@@ -61990,20 +62274,20 @@
         <v>225</v>
       </c>
     </row>
-    <row r="7" spans="2:52" ht="26">
+    <row r="7" spans="2:52" ht="27">
       <c r="B7" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="285" t="s">
+      <c r="C7" s="309" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="283"/>
-      <c r="E7" s="283"/>
-      <c r="F7" s="283"/>
-      <c r="G7" s="283"/>
-      <c r="H7" s="283"/>
-      <c r="I7" s="283"/>
-      <c r="J7" s="284"/>
+      <c r="D7" s="307"/>
+      <c r="E7" s="307"/>
+      <c r="F7" s="307"/>
+      <c r="G7" s="307"/>
+      <c r="H7" s="307"/>
+      <c r="I7" s="307"/>
+      <c r="J7" s="308"/>
       <c r="K7" s="187" t="s">
         <v>285</v>
       </c>
@@ -62018,7 +62302,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="2:52" ht="62">
+    <row r="8" spans="2:52" ht="64.5">
       <c r="B8" s="64" t="s">
         <v>28</v>
       </c>
@@ -62062,7 +62346,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="2:52" ht="65.5" thickBot="1">
+    <row r="9" spans="2:52" ht="68.25" thickBot="1">
       <c r="B9" s="66" t="s">
         <v>30</v>
       </c>
@@ -62110,7 +62394,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="10" spans="2:52" ht="13.5" thickTop="1">
+    <row r="10" spans="2:52" ht="14.25" thickTop="1">
       <c r="B10" s="67" t="s">
         <v>241</v>
       </c>
@@ -62446,7 +62730,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="17" spans="2:17" ht="13.5" thickBot="1">
+    <row r="17" spans="2:17" ht="14.25" thickBot="1">
       <c r="B17" s="191" t="s">
         <v>271</v>
       </c>
@@ -62617,14 +62901,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="78" t="s">
         <v>85</v>
       </c>
@@ -62634,7 +62918,7 @@
       </c>
       <c r="D2" s="79"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="72" t="s">
         <v>85</v>
       </c>
@@ -62645,7 +62929,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -62656,7 +62940,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -62667,7 +62951,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -62678,7 +62962,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -62689,7 +62973,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -62711,7 +62995,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -62722,7 +63006,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -62733,7 +63017,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -62744,7 +63028,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -62755,7 +63039,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -62766,7 +63050,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -62788,7 +63072,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -62799,7 +63083,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -62810,7 +63094,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -62843,7 +63127,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26">
+    <row r="22" spans="2:4" ht="27">
       <c r="B22" s="2">
         <v>18</v>
       </c>
@@ -62854,7 +63138,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="26">
+    <row r="23" spans="2:4" ht="27">
       <c r="B23" s="2">
         <v>19</v>
       </c>
@@ -62880,7 +63164,7 @@
       <c r="C26" s="82"/>
       <c r="D26" s="68"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="83"/>
       <c r="D27" s="5"/>
